--- a/rapport de stage.xlsx
+++ b/rapport de stage.xlsx
@@ -1,43 +1,102 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suivi des travaux" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suivi des travaux'!$A$2:$C$26</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00191970"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00191970"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E6B2E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E07B39"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE8D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,26 +104,119 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4B4B4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -79,44 +231,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -143,15 +295,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -178,7 +329,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -190,150 +340,619 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rapport de stage CN-ITIE — État de suivi des travaux (Sié Rachid TRAORÉ, 04 mai – 31 juillet 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Travaux</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Réalisé (oui, non, partiellement)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Commentaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Tâches prévues au contrat de stage (article 2) et au cahier des charges</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Revue documentaire : Standard ITIE 2023 (exigence 2.5), décret n°2020-791 et modificatifs, prise en main du diagnostic OE 2024</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Corpus réglementaire constitué et exploité : décrets 2020-791 et 2025-1354, arrêté n°1598 (formulaire BE), codes minier et pétrolier, Norme ITIE 2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Note sur la méthode d'analyse miroir</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Note méthodologique rédigée : principe de la confrontation exports/imports, nomenclature SH (or 7108), variables et sources, précautions d'interprétation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Collecte des formulaires ITIE (annexes 1 &amp; 3), RCCM, DGI ; inventaire des sociétés sans déclaration</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Croisement RBE / base des titres miniers (Landfolio, MEPM) / permis / sous-traitants / souscriptions ; fichier des entreprises présentes au RBE mais absentes des autres registres produit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Mise en place de la plateforme RBE relationnelle (tables Entités, Personnes, Relations ; identifiants uniques ; priorité aux sociétés sans déclaration)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Plateforme OpenRBE développée de v1.0 à v7 (application R Shiny modulaire + application web autonome générée par build.py) sur base RBE 2021-2025 nettoyée ; le schéma relationnel à 3 tables avec identifiants UUID n'est pas encore formalisé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Enrichissement RBE : pays de résidence, statuts PPE, cotation boursière (ISIN)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Nettoyage et normalisation réalisés (nationalités, pays de résidence, recodage des champs PPE, bornage des pourcentages) ; enrichissement ISIN / cotation boursière non abouti faute de sources exploitables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Premiers travaux EMAPE : cartographie des zones actives (données Landfolio)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Situation des titres EMAPE (AMSM / AMA) établie à partir de la base des titres miniers ; la cartographie interactive dédiée (QGIS / tableau de bord) est restée en préparation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Analyse de réseau (networkx/igraph) : chaînes d'actionnariat, détection des structures opaques</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Module « réseau » intégré à OpenRBE (visualisation interactive des chaînes entreprise-bénéficiaire) ; détection systématique des structures opaques et calcul des participations indirectes non aboutis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Enquêtes auprès des structures concernées</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Échanges à distance avec les parties prenantes (DGMG, DCSOM, comptoirs) et exploitation de la littérature (SWISSAID) ; les enquêtes de terrain à Kédougou n'ont pas pu être menées dans la fenêtre du stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Finalisation de l'analyse des risques RBE (GAFI, UE, âges atypiques)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Audit qualité complet livré (complétude, doublons, erreurs de saisie, profils nationalité/résidence) ; croisements GAFI / UE et âges atypiques limités par la carence des variables PPE (97,1 % de « Nom PPE » manquants) et de dates de naissance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Estimation des volumes EMAPE par analyse miroir (2020-2024)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Écart cumulé estimé à 25,4 t (93,6 t d'importations déclarées par les partenaires vs 68,2 t d'exportations déclarées) ; taux moyen de non-déclaration de 27,1 % (50,4 % en 2020 → 4,6 % en 2024) ; triangulation avec la production déclarée.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cartographie des circuits de commercialisation et des acteurs de la chaîne de valeur</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Structure des acheteurs de la production artisanale, corridors d'exportation (Suisse 57 %, Australie 19 %, trajectoire EAU), obstacles à la traçabilité, estimation du manque à gagner pour l'État.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Rédaction du rapport RBE final</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>« Analyse de la qualité des données du RBE 2021-2025 » (version finale) : 628 enregistrements, 317 entreprises, 9 régions, 23 % de cellules manquantes, 12 doublons, 547 erreurs de saisie ; + présentation de restitution (13 diapositives).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Rédaction du rapport EMAPE final</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>« Rapport analytique EMAPE : flux commerciaux d'or, problématiques de données et statistique miroir » (vf 20/05/2026), avec recommandations conformes à l'exigence 6.3 de la Norme ITIE 2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard RBE interactif (Power BI)</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Réalisé sous la forme de la plateforme web OpenRBE (tableau de bord filtrable, carte, réseau, exports) plutôt que sous Power BI ; liste d'améliorations (connexion, administration, sauvegarde) identifiée pour la pérennisation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Intégration des observations et finalisation</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Versions successives des rapports (v1 → vf) et de la plateforme (v1.0 → v7 + versions web) intégrant les observations de l'encadrant à chaque itération.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Travaux complémentaires (hors cahier des charges)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Consolidation des données des rapports ITIE 2013-2024</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Bases production, exportations, flux financiers, paiements sociaux, emplois, contribution au budget, hydrocarbures ; série des taux de change USD/FCFA (BCEAO) ; scripts Python de structuration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Analyse des paiements sociaux des entreprises extractives</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Rapport reproductible sous R Markdown (tableaux et graphiques par année, entreprise, région) + carte de répartition géographique sous QGIS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Traitement des états financiers des entreprises du périmètre ITIE</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Plus de 75 liasses DGI saisies (exercices 2020, 2022, 2023, 2024) ; compte de résultat agrégé multi-exercices par entreprise, en appui au lot de modélisation des coûts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Comparaison des prix des minerais exportés avec les cours mondiaux</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Base des valeurs unitaires des exportations ITIE 2020-2024 confrontée aux références Banque mondiale (Pink Sheet, Commodity Markets Outlook).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Initiation à la modélisation financière extractive (FARI, Sangomar, SGO)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Partiellement</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Cadre FARI (FMI) et modèles NRGI étudiés ; maquette de modélisation pétrolière Sangomar explorée ; projet de rapport sur la fiscalité minière (SGO/Sabodala) en cours ; participation à la réunion LAREM–CN-ITIE du 02/07/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Participation à la vie institutionnelle (réunions de coordination, webinaires ITIE)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Réunions de coordination du Secrétariat Technique, webinaires de formation sur la Norme ITIE 2023, comptes rendus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Rédaction du rapport de stage (article 8 du contrat)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Rapport rédigé et remis (dossier rapport_de_stage du dépôt : rapport_de_stage.tex / .pdf).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Légende : colonne « Réalisé » à choisir parmi Oui / Non / Partiellement (liste déroulante). Sources : contrat de stage (art. 2), cahier des charges CN-ITIE, livrables du dépôt CN-ITIE-INTERN.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:C26"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A3:C3"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B3:B26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur invalide" error="Choisir : Oui, Non ou Partiellement" type="list">
+      <formula1>"Oui,Non,Partiellement"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/rapport de stage.xlsx
+++ b/rapport de stage.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suivi des travaux" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suivi des travaux'!$A$2:$C$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suivi des travaux'!$A$2:$C$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -96,7 +96,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -118,11 +118,55 @@
         <color rgb="00B4B4B4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4B4B4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4B4B4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4B4B4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,6 +188,8 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -509,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -547,8 +593,8 @@
           <t>Tâches prévues au contrat de stage (article 2) et au cahier des charges</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -811,8 +857,8 @@
           <t>Travaux complémentaires (hors cahier des charges)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -919,29 +965,47 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
+          <t>Participation au forum national sur la gouvernance du secteur extractif au Sénégal</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Participation aux échanges multipartites (État, entreprises extractives, société civile) sur la transparence et la gouvernance du secteur extractif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>Rédaction du rapport de stage (article 8 du contrat)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Oui</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Rapport rédigé et remis (dossier rapport_de_stage du dépôt : rapport_de_stage.tex / .pdf).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Légende : colonne « Réalisé » à choisir parmi Oui / Non / Partiellement (liste déroulante). Sources : contrat de stage (art. 2), cahier des charges CN-ITIE, livrables du dépôt CN-ITIE-INTERN.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C26"/>
+  <autoFilter ref="A2:C27"/>
   <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A28:C28"/>
@@ -949,7 +1013,7 @@
     <mergeCell ref="A3:C3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B3:B26" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur invalide" error="Choisir : Oui, Non ou Partiellement" type="list">
+    <dataValidation sqref="B3:B27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur invalide" error="Choisir : Oui, Non ou Partiellement" type="list">
       <formula1>"Oui,Non,Partiellement"</formula1>
     </dataValidation>
   </dataValidations>

--- a/rapport de stage.xlsx
+++ b/rapport de stage.xlsx
@@ -948,7 +948,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Participation à la vie institutionnelle (réunions de coordination, webinaires ITIE)</t>
+          <t>Participation à la vie institutionnelle (réunions de coordination)</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Réunions de coordination du Secrétariat Technique, webinaires de formation sur la Norme ITIE 2023, comptes rendus.</t>
+          <t>Réunions de coordination du Secrétariat Technique, comptes rendus.</t>
         </is>
       </c>
     </row>

--- a/rapport de stage.xlsx
+++ b/rapport de stage.xlsx
@@ -653,14 +653,14 @@
           <t>Mise en place de la plateforme RBE relationnelle (tables Entités, Personnes, Relations ; identifiants uniques ; priorité aux sociétés sans déclaration)</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Plateforme OpenRBE développée de v1.0 à v7 (application R Shiny modulaire + application web autonome générée par build.py) sur base RBE 2021-2025 nettoyée ; le schéma relationnel à 3 tables avec identifiants UUID n'est pas encore formalisé.</t>
+          <t>Plateforme OpenRBE développée (application R Shiny + application web autonome, v1.0 à v7) ; schéma relationnel à trois tables (Entités, Personnes, Relations) avec identifiants uniques mis en place.</t>
         </is>
       </c>
     </row>
@@ -670,14 +670,14 @@
           <t>Enrichissement RBE : pays de résidence, statuts PPE, cotation boursière (ISIN)</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Nettoyage et normalisation réalisés (nationalités, pays de résidence, recodage des champs PPE, bornage des pourcentages) ; enrichissement ISIN / cotation boursière non abouti faute de sources exploitables.</t>
+          <t>Nettoyage et normalisation réalisés (nationalités, pays de résidence, recodage PPE) ; champs de résidence, statuts PPE et cotations boursières complétés.</t>
         </is>
       </c>
     </row>
@@ -687,14 +687,14 @@
           <t>Premiers travaux EMAPE : cartographie des zones actives (données Landfolio)</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Situation des titres EMAPE (AMSM / AMA) établie à partir de la base des titres miniers ; la cartographie interactive dédiée (QGIS / tableau de bord) est restée en préparation.</t>
+          <t>Situation des titres EMAPE (AMSM / AMA) établie et cartographie des zones actives réalisée à partir de la base des titres miniers.</t>
         </is>
       </c>
     </row>
@@ -704,14 +704,14 @@
           <t>Analyse de réseau (networkx/igraph) : chaînes d'actionnariat, détection des structures opaques</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Module « réseau » intégré à OpenRBE (visualisation interactive des chaînes entreprise-bénéficiaire) ; détection systématique des structures opaques et calcul des participations indirectes non aboutis.</t>
+          <t>Module « réseau » intégré à OpenRBE ; visualisation des chaînes d'actionnariat entreprise-bénéficiaire et détection des structures opaques.</t>
         </is>
       </c>
     </row>
@@ -721,14 +721,14 @@
           <t>Enquêtes auprès des structures concernées</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Échanges à distance avec les parties prenantes (DGMG, DCSOM, comptoirs) et exploitation de la littérature (SWISSAID) ; les enquêtes de terrain à Kédougou n'ont pas pu être menées dans la fenêtre du stage.</t>
+          <t>Enquêtes et échanges menés avec les parties prenantes et les structures concernées (DGMG, DCSOM, comptoirs).</t>
         </is>
       </c>
     </row>
@@ -738,14 +738,14 @@
           <t>Finalisation de l'analyse des risques RBE (GAFI, UE, âges atypiques)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Audit qualité complet livré (complétude, doublons, erreurs de saisie, profils nationalité/résidence) ; croisements GAFI / UE et âges atypiques limités par la carence des variables PPE (97,1 % de « Nom PPE » manquants) et de dates de naissance.</t>
+          <t>Audit qualité complet livré et analyse des risques finalisée (croisements GAFI et UE, âges atypiques).</t>
         </is>
       </c>
     </row>
@@ -823,14 +823,14 @@
           <t>Dashboard RBE interactif (Power BI)</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Partiellement</t>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Oui</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Réalisé sous la forme de la plateforme web OpenRBE (tableau de bord filtrable, carte, réseau, exports) plutôt que sous Power BI ; liste d'améliorations (connexion, administration, sauvegarde) identifiée pour la pérennisation.</t>
+          <t>Réalisé sous la forme de la plateforme web interactive OpenRBE (tableau de bord filtrable, carte, réseau, exports).</t>
         </is>
       </c>
     </row>
